--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="339">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -64,10 +64,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -221,6 +218,15 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
+</t>
+  </si>
+  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1049,22 +1055,19 @@
     <t>dbuf</t>
   </si>
   <si>
+    <t>vbuffer</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>delayfixed</t>
+  </si>
+  <si>
+    <t>amux8</t>
+  </si>
+  <si>
     <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>vbuffer</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>delayfixed</t>
-  </si>
-  <si>
-    <t>amux8</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
 </sst>
 </file>
@@ -1435,7 +1438,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1455,7 +1458,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1475,7 +1478,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1490,7 +1493,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1505,7 +1508,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1525,12 +1528,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1545,12 +1548,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1565,12 +1568,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1588,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1600,131 +1603,136 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3353,7 +3361,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3451,7 +3459,7 @@
         <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3483,14 +3491,6 @@
         <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>339</v>
-      </c>
-      <c r="B19" t="s">
         <v>312</v>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3517,11 +3517,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3536,7 +3531,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3546,22 +3541,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3576,7 +3571,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3586,7 +3581,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3601,7 +3596,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3611,7 +3606,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3626,7 +3621,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3636,7 +3631,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3651,7 +3646,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3661,7 +3656,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3676,7 +3671,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="341">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -64,7 +64,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -219,10 +222,10 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
 4 error(s) during elaboration.
 </t>
   </si>
@@ -1055,6 +1058,9 @@
     <t>dbuf</t>
   </si>
   <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1067,7 +1073,7 @@
     <t>amux8</t>
   </si>
   <si>
-    <t>PEBBLEtielo</t>
+    <t>PEBBLEtiehi</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1444,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1458,7 +1464,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1478,7 +1484,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1493,7 +1499,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +1514,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1528,12 +1534,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1548,12 +1554,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1568,12 +1574,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1588,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1608,132 +1614,132 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1748,7 +1754,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1793,17 +1799,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1818,7 +1824,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1838,17 +1844,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1863,17 +1869,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1888,81 +1894,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
         <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
         <v>81</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1970,185 +1976,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2156,445 +2162,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B89" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2602,628 +2608,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B105" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B107" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B108" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B109" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B110" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B111" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B116" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B117" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B118" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B119" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B120" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B121" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B125" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B126" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B127" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B128" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B129" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B135" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B136" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B137" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B138" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B139" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B140" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B148" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B149" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B150" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B152" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B153" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B154" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B155" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B157" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B159" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B160" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B161" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B162" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B163" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B164" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B167" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B168" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B169" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B170" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B171" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B172" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B174" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B176" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B178" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B179" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3238,47 +3244,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3286,15 +3292,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3302,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3317,7 +3323,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -3332,26 +3338,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3361,12 +3367,12 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3376,122 +3382,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" t="s">
-        <v>312</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -3501,7 +3515,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3517,6 +3531,11 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3531,7 +3550,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3541,22 +3560,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3571,7 +3590,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3581,7 +3600,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3596,7 +3615,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3606,7 +3625,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3621,7 +3640,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3631,7 +3650,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3646,7 +3665,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3656,7 +3675,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -3671,7 +3690,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="339">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -49,10 +49,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -221,15 +218,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1037,10 +1025,10 @@
     <t>14</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
     <t>nand2</t>
-  </si>
-  <si>
-    <t>noconn</t>
   </si>
   <si>
     <t>wrapper</t>
@@ -1444,7 +1432,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1464,7 +1452,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1484,7 +1472,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1499,7 +1487,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1514,7 +1502,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1534,12 +1522,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1554,12 +1542,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1574,12 +1562,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1594,7 +1582,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1609,137 +1597,132 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +1737,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1799,17 +1782,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1824,7 +1807,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1844,17 +1827,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1869,17 +1852,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1894,81 +1877,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1976,185 +1959,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2162,445 +2145,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B80" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2608,628 +2591,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B105" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B106" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B107" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B109" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B110" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B111" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B116" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B117" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B118" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B119" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B120" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B121" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B125" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B127" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B128" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B129" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B135" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B136" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B137" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B138" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B148" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B149" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B150" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B151" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B152" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B153" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B154" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B155" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B156" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B157" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B158" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B159" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B160" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B161" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B162" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B163" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B164" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B168" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B169" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B170" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B171" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B172" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3244,47 +3227,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3292,15 +3275,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3308,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3323,7 +3306,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3338,26 +3321,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3372,7 +3355,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3382,130 +3365,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3565,17 +3548,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3590,7 +3573,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3600,7 +3583,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3615,7 +3598,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3625,7 +3608,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3640,7 +3623,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3650,7 +3633,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3665,7 +3648,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3675,7 +3658,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3690,7 +3673,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="340">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -215,6 +215,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1597,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1723,6 +1732,11 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1737,7 +1751,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1782,17 +1796,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1807,7 +1821,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1827,17 +1841,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1852,17 +1866,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1877,81 +1891,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1959,185 +1973,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2145,445 +2159,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2591,628 +2605,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B124" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B130" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B131" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B156" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B173" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3227,47 +3241,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3275,15 +3289,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3291,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3306,7 +3320,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3321,26 +3335,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3355,7 +3369,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3365,130 +3379,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="339">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -215,15 +215,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1606,7 +1597,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1732,11 +1723,6 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1751,7 +1737,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1796,17 +1782,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1821,7 +1807,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1841,17 +1827,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1866,17 +1852,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1891,81 +1877,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
         <v>71</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1973,185 +1959,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
         <v>96</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" t="s">
         <v>105</v>
-      </c>
-      <c r="B35" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s">
         <v>107</v>
-      </c>
-      <c r="B36" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2159,445 +2145,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
         <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s">
         <v>121</v>
-      </c>
-      <c r="B48" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
         <v>125</v>
-      </c>
-      <c r="B51" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
         <v>128</v>
-      </c>
-      <c r="B54" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" t="s">
         <v>130</v>
-      </c>
-      <c r="B55" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" t="s">
         <v>138</v>
-      </c>
-      <c r="B63" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" t="s">
         <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
         <v>144</v>
-      </c>
-      <c r="B67" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" t="s">
         <v>156</v>
-      </c>
-      <c r="B79" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
         <v>158</v>
-      </c>
-      <c r="B80" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>167</v>
+      </c>
+      <c r="B89" t="s">
         <v>168</v>
-      </c>
-      <c r="B89" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2605,628 +2591,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" t="s">
         <v>184</v>
-      </c>
-      <c r="B105" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
+        <v>185</v>
+      </c>
+      <c r="B106" t="s">
         <v>186</v>
-      </c>
-      <c r="B106" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" t="s">
         <v>188</v>
-      </c>
-      <c r="B107" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>189</v>
+      </c>
+      <c r="B108" t="s">
         <v>190</v>
-      </c>
-      <c r="B108" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>191</v>
+      </c>
+      <c r="B109" t="s">
         <v>192</v>
-      </c>
-      <c r="B109" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>193</v>
+      </c>
+      <c r="B110" t="s">
         <v>194</v>
-      </c>
-      <c r="B110" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>195</v>
+      </c>
+      <c r="B111" t="s">
         <v>196</v>
-      </c>
-      <c r="B111" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
+        <v>200</v>
+      </c>
+      <c r="B116" t="s">
         <v>201</v>
-      </c>
-      <c r="B116" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" t="s">
         <v>203</v>
-      </c>
-      <c r="B117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>204</v>
+      </c>
+      <c r="B118" t="s">
         <v>205</v>
-      </c>
-      <c r="B118" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>206</v>
+      </c>
+      <c r="B119" t="s">
         <v>207</v>
-      </c>
-      <c r="B119" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>208</v>
+      </c>
+      <c r="B120" t="s">
         <v>209</v>
-      </c>
-      <c r="B120" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>210</v>
+      </c>
+      <c r="B121" t="s">
         <v>211</v>
-      </c>
-      <c r="B121" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125" t="s">
         <v>216</v>
-      </c>
-      <c r="B125" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
+        <v>217</v>
+      </c>
+      <c r="B126" t="s">
         <v>218</v>
-      </c>
-      <c r="B126" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>219</v>
+      </c>
+      <c r="B127" t="s">
         <v>220</v>
-      </c>
-      <c r="B127" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>221</v>
+      </c>
+      <c r="B128" t="s">
         <v>222</v>
-      </c>
-      <c r="B128" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>223</v>
+      </c>
+      <c r="B129" t="s">
         <v>224</v>
-      </c>
-      <c r="B129" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>230</v>
+      </c>
+      <c r="B135" t="s">
         <v>231</v>
-      </c>
-      <c r="B135" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" t="s">
         <v>233</v>
-      </c>
-      <c r="B136" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
+        <v>234</v>
+      </c>
+      <c r="B137" t="s">
         <v>235</v>
-      </c>
-      <c r="B137" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>236</v>
+      </c>
+      <c r="B138" t="s">
         <v>237</v>
-      </c>
-      <c r="B138" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>238</v>
+      </c>
+      <c r="B139" t="s">
         <v>239</v>
-      </c>
-      <c r="B139" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
+        <v>248</v>
+      </c>
+      <c r="B148" t="s">
         <v>249</v>
-      </c>
-      <c r="B148" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>250</v>
+      </c>
+      <c r="B149" t="s">
         <v>251</v>
-      </c>
-      <c r="B149" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B150" t="s">
         <v>253</v>
-      </c>
-      <c r="B150" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>254</v>
+      </c>
+      <c r="B151" t="s">
         <v>255</v>
-      </c>
-      <c r="B151" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>256</v>
+      </c>
+      <c r="B152" t="s">
         <v>257</v>
-      </c>
-      <c r="B152" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>258</v>
+      </c>
+      <c r="B153" t="s">
         <v>259</v>
-      </c>
-      <c r="B153" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>260</v>
+      </c>
+      <c r="B154" t="s">
         <v>261</v>
-      </c>
-      <c r="B154" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>262</v>
+      </c>
+      <c r="B155" t="s">
         <v>263</v>
-      </c>
-      <c r="B155" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>264</v>
+      </c>
+      <c r="B156" t="s">
         <v>265</v>
-      </c>
-      <c r="B156" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>266</v>
+      </c>
+      <c r="B157" t="s">
         <v>267</v>
-      </c>
-      <c r="B157" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>268</v>
+      </c>
+      <c r="B158" t="s">
         <v>269</v>
-      </c>
-      <c r="B158" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>270</v>
+      </c>
+      <c r="B159" t="s">
         <v>271</v>
-      </c>
-      <c r="B159" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" t="s">
         <v>273</v>
-      </c>
-      <c r="B160" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>274</v>
+      </c>
+      <c r="B161" t="s">
         <v>275</v>
-      </c>
-      <c r="B161" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>276</v>
+      </c>
+      <c r="B162" t="s">
         <v>277</v>
-      </c>
-      <c r="B162" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>278</v>
+      </c>
+      <c r="B163" t="s">
         <v>279</v>
-      </c>
-      <c r="B163" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>280</v>
+      </c>
+      <c r="B164" t="s">
         <v>281</v>
-      </c>
-      <c r="B164" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>285</v>
+      </c>
+      <c r="B168" t="s">
         <v>286</v>
-      </c>
-      <c r="B168" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>287</v>
+      </c>
+      <c r="B169" t="s">
         <v>288</v>
-      </c>
-      <c r="B169" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>289</v>
+      </c>
+      <c r="B170" t="s">
         <v>290</v>
-      </c>
-      <c r="B170" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>291</v>
+      </c>
+      <c r="B171" t="s">
         <v>292</v>
-      </c>
-      <c r="B171" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>293</v>
+      </c>
+      <c r="B172" t="s">
         <v>294</v>
-      </c>
-      <c r="B172" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
+        <v>300</v>
+      </c>
+      <c r="B178" t="s">
         <v>301</v>
-      </c>
-      <c r="B178" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3241,47 +3227,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3289,15 +3275,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3305,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3320,7 +3306,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3335,26 +3321,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3369,7 +3355,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3379,130 +3365,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" t="s">
         <v>323</v>
-      </c>
-      <c r="B5" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
         <v>325</v>
-      </c>
-      <c r="B6" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="338">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -49,31 +49,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -1025,10 +1025,13 @@
     <t>14</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>nand2</t>
+    <t>PEBBLEtielo</t>
   </si>
   <si>
     <t>wrapper</t>
@@ -1046,9 +1049,6 @@
     <t>dbuf</t>
   </si>
   <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1059,9 +1059,6 @@
   </si>
   <si>
     <t>amux8</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
 </sst>
 </file>
@@ -3350,7 +3347,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3392,7 +3389,7 @@
         <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3400,7 +3397,7 @@
         <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3408,7 +3405,7 @@
         <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3480,14 +3477,6 @@
         <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>338</v>
-      </c>
-      <c r="B19" t="s">
         <v>311</v>
       </c>
     </row>
@@ -3498,7 +3487,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3514,11 +3503,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3533,7 +3517,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3543,12 +3527,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="339">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -215,6 +215,14 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
 </t>
   </si>
   <si>
@@ -1594,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1720,6 +1728,11 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1747,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1779,17 +1792,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1804,7 +1817,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1824,17 +1837,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1849,17 +1862,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1874,81 +1887,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1956,185 +1969,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2142,445 +2155,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2588,628 +2601,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B124" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B130" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B131" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B156" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B173" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3224,47 +3237,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3272,15 +3285,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3288,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3303,7 +3316,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3318,26 +3331,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3352,7 +3365,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3362,122 +3375,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -219,10 +219,11 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="338">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -215,15 +215,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1603,7 +1594,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1729,11 +1720,6 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1748,7 +1734,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1793,17 +1779,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1818,7 +1804,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1838,17 +1824,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1863,17 +1849,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1888,81 +1874,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
         <v>71</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1970,185 +1956,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
         <v>96</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" t="s">
         <v>105</v>
-      </c>
-      <c r="B35" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s">
         <v>107</v>
-      </c>
-      <c r="B36" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2156,445 +2142,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
         <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s">
         <v>121</v>
-      </c>
-      <c r="B48" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
         <v>125</v>
-      </c>
-      <c r="B51" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
         <v>128</v>
-      </c>
-      <c r="B54" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" t="s">
         <v>130</v>
-      </c>
-      <c r="B55" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" t="s">
         <v>138</v>
-      </c>
-      <c r="B63" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" t="s">
         <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
         <v>144</v>
-      </c>
-      <c r="B67" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" t="s">
         <v>156</v>
-      </c>
-      <c r="B79" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
         <v>158</v>
-      </c>
-      <c r="B80" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>167</v>
+      </c>
+      <c r="B89" t="s">
         <v>168</v>
-      </c>
-      <c r="B89" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2602,628 +2588,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" t="s">
         <v>184</v>
-      </c>
-      <c r="B105" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
+        <v>185</v>
+      </c>
+      <c r="B106" t="s">
         <v>186</v>
-      </c>
-      <c r="B106" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" t="s">
         <v>188</v>
-      </c>
-      <c r="B107" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>189</v>
+      </c>
+      <c r="B108" t="s">
         <v>190</v>
-      </c>
-      <c r="B108" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>191</v>
+      </c>
+      <c r="B109" t="s">
         <v>192</v>
-      </c>
-      <c r="B109" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>193</v>
+      </c>
+      <c r="B110" t="s">
         <v>194</v>
-      </c>
-      <c r="B110" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>195</v>
+      </c>
+      <c r="B111" t="s">
         <v>196</v>
-      </c>
-      <c r="B111" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
+        <v>200</v>
+      </c>
+      <c r="B116" t="s">
         <v>201</v>
-      </c>
-      <c r="B116" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" t="s">
         <v>203</v>
-      </c>
-      <c r="B117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>204</v>
+      </c>
+      <c r="B118" t="s">
         <v>205</v>
-      </c>
-      <c r="B118" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>206</v>
+      </c>
+      <c r="B119" t="s">
         <v>207</v>
-      </c>
-      <c r="B119" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>208</v>
+      </c>
+      <c r="B120" t="s">
         <v>209</v>
-      </c>
-      <c r="B120" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>210</v>
+      </c>
+      <c r="B121" t="s">
         <v>211</v>
-      </c>
-      <c r="B121" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125" t="s">
         <v>216</v>
-      </c>
-      <c r="B125" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
+        <v>217</v>
+      </c>
+      <c r="B126" t="s">
         <v>218</v>
-      </c>
-      <c r="B126" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>219</v>
+      </c>
+      <c r="B127" t="s">
         <v>220</v>
-      </c>
-      <c r="B127" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>221</v>
+      </c>
+      <c r="B128" t="s">
         <v>222</v>
-      </c>
-      <c r="B128" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>223</v>
+      </c>
+      <c r="B129" t="s">
         <v>224</v>
-      </c>
-      <c r="B129" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>230</v>
+      </c>
+      <c r="B135" t="s">
         <v>231</v>
-      </c>
-      <c r="B135" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" t="s">
         <v>233</v>
-      </c>
-      <c r="B136" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
+        <v>234</v>
+      </c>
+      <c r="B137" t="s">
         <v>235</v>
-      </c>
-      <c r="B137" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>236</v>
+      </c>
+      <c r="B138" t="s">
         <v>237</v>
-      </c>
-      <c r="B138" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>238</v>
+      </c>
+      <c r="B139" t="s">
         <v>239</v>
-      </c>
-      <c r="B139" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
+        <v>248</v>
+      </c>
+      <c r="B148" t="s">
         <v>249</v>
-      </c>
-      <c r="B148" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>250</v>
+      </c>
+      <c r="B149" t="s">
         <v>251</v>
-      </c>
-      <c r="B149" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B150" t="s">
         <v>253</v>
-      </c>
-      <c r="B150" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>254</v>
+      </c>
+      <c r="B151" t="s">
         <v>255</v>
-      </c>
-      <c r="B151" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>256</v>
+      </c>
+      <c r="B152" t="s">
         <v>257</v>
-      </c>
-      <c r="B152" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>258</v>
+      </c>
+      <c r="B153" t="s">
         <v>259</v>
-      </c>
-      <c r="B153" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>260</v>
+      </c>
+      <c r="B154" t="s">
         <v>261</v>
-      </c>
-      <c r="B154" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>262</v>
+      </c>
+      <c r="B155" t="s">
         <v>263</v>
-      </c>
-      <c r="B155" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>264</v>
+      </c>
+      <c r="B156" t="s">
         <v>265</v>
-      </c>
-      <c r="B156" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>266</v>
+      </c>
+      <c r="B157" t="s">
         <v>267</v>
-      </c>
-      <c r="B157" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>268</v>
+      </c>
+      <c r="B158" t="s">
         <v>269</v>
-      </c>
-      <c r="B158" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>270</v>
+      </c>
+      <c r="B159" t="s">
         <v>271</v>
-      </c>
-      <c r="B159" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" t="s">
         <v>273</v>
-      </c>
-      <c r="B160" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>274</v>
+      </c>
+      <c r="B161" t="s">
         <v>275</v>
-      </c>
-      <c r="B161" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>276</v>
+      </c>
+      <c r="B162" t="s">
         <v>277</v>
-      </c>
-      <c r="B162" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>278</v>
+      </c>
+      <c r="B163" t="s">
         <v>279</v>
-      </c>
-      <c r="B163" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>280</v>
+      </c>
+      <c r="B164" t="s">
         <v>281</v>
-      </c>
-      <c r="B164" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>285</v>
+      </c>
+      <c r="B168" t="s">
         <v>286</v>
-      </c>
-      <c r="B168" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>287</v>
+      </c>
+      <c r="B169" t="s">
         <v>288</v>
-      </c>
-      <c r="B169" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>289</v>
+      </c>
+      <c r="B170" t="s">
         <v>290</v>
-      </c>
-      <c r="B170" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>291</v>
+      </c>
+      <c r="B171" t="s">
         <v>292</v>
-      </c>
-      <c r="B171" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>293</v>
+      </c>
+      <c r="B172" t="s">
         <v>294</v>
-      </c>
-      <c r="B172" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
+        <v>300</v>
+      </c>
+      <c r="B178" t="s">
         <v>301</v>
-      </c>
-      <c r="B178" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3238,47 +3224,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3286,15 +3272,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3302,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3317,7 +3303,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3332,26 +3318,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3366,7 +3352,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3376,122 +3362,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" t="s">
         <v>323</v>
-      </c>
-      <c r="B5" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
         <v>325</v>
-      </c>
-      <c r="B6" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="341">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_negative</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -215,6 +221,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1429,7 +1444,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1449,7 +1464,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1469,7 +1484,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1484,7 +1499,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1499,7 +1514,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1519,12 +1534,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1539,12 +1554,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1559,12 +1574,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1579,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1594,132 +1609,137 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1754,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1779,17 +1799,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1804,7 +1824,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1824,17 +1844,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1849,17 +1869,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1874,81 +1894,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1956,185 +1976,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2142,445 +2162,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" t="s">
         <v>145</v>
-      </c>
-      <c r="B68" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2588,628 +2608,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
+        <v>217</v>
+      </c>
+      <c r="B124" t="s">
         <v>214</v>
-      </c>
-      <c r="B124" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B127" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B130" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B131" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B149" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B151" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B152" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B156" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B157" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B159" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B160" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B161" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B168" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B171" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B172" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B173" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B179" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3224,47 +3244,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3272,15 +3292,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3288,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -3303,7 +3323,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -3318,26 +3338,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3352,7 +3372,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3362,122 +3382,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3512,7 +3532,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3543,6 +3563,16 @@
     <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3557,7 +3587,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3567,7 +3597,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3582,7 +3612,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3592,7 +3622,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3607,7 +3637,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3617,7 +3647,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3632,7 +3662,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3642,7 +3672,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3657,7 +3687,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="337">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -49,10 +49,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -71,15 +71,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_negative</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -224,15 +215,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1040,28 +1022,28 @@
     <t>14</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
     <t>nand2</t>
   </si>
   <si>
-    <t>noconn</t>
+    <t>wrapper</t>
+  </si>
+  <si>
+    <t>switchpulldown</t>
+  </si>
+  <si>
+    <t>switchgnd</t>
+  </si>
+  <si>
+    <t>nand3</t>
+  </si>
+  <si>
+    <t>dbuf</t>
   </si>
   <si>
     <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>wrapper</t>
-  </si>
-  <si>
-    <t>switchpulldown</t>
-  </si>
-  <si>
-    <t>switchgnd</t>
-  </si>
-  <si>
-    <t>nand3</t>
-  </si>
-  <si>
-    <t>dbuf</t>
   </si>
   <si>
     <t>vbuffer</t>
@@ -1444,7 +1426,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1464,7 +1446,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1484,7 +1466,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1499,7 +1481,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1514,7 +1496,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1534,12 +1516,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1554,12 +1536,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1574,12 +1556,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1594,7 +1576,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1609,137 +1591,132 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +1731,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1799,17 +1776,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1824,7 +1801,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1844,17 +1821,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1869,17 +1846,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1894,81 +1871,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1976,185 +1953,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2162,445 +2139,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B80" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B90" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B91" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B97" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B99" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2608,628 +2585,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B101" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B105" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B106" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B107" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B108" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B109" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B110" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B111" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B115" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B116" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B117" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B118" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B120" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B121" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B122" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B123" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B124" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B125" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B126" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B127" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B128" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B129" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B130" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B131" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B132" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B133" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B134" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B135" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B136" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B137" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B138" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B139" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B140" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B141" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B142" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B143" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B144" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B145" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B146" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B147" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B148" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B149" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B150" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B151" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B152" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B153" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B154" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B155" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B156" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B157" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B158" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B159" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B160" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B161" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B162" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B163" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B164" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B166" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B167" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B168" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B169" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B170" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B171" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B172" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B173" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B174" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B175" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B176" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B177" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B178" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B179" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3244,47 +3221,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3292,15 +3269,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3308,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3323,7 +3300,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3338,26 +3315,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3372,7 +3349,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3382,122 +3359,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B7" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B16" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B17" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3532,7 +3509,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3552,27 +3529,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3587,7 +3554,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3597,7 +3564,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3612,7 +3579,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3622,7 +3589,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3637,7 +3604,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3647,7 +3614,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3662,7 +3629,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3672,7 +3639,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3687,7 +3654,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="338">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -49,28 +49,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -1022,10 +1025,10 @@
     <t>14</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
     <t>noconn</t>
-  </si>
-  <si>
-    <t>nand2</t>
   </si>
   <si>
     <t>wrapper</t>
@@ -1426,7 +1429,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1446,7 +1449,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1466,7 +1469,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1481,7 +1484,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1496,7 +1499,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1516,12 +1519,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1536,12 +1539,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1556,12 +1559,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1576,7 +1579,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1596,127 +1599,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1731,7 +1734,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1776,17 +1779,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1801,7 +1804,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1821,17 +1824,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1846,17 +1849,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1871,81 +1874,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
         <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
         <v>79</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1953,185 +1956,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2139,445 +2142,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2585,628 +2588,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B108" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3221,47 +3224,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3269,15 +3272,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3285,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3300,7 +3303,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3315,26 +3318,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3349,7 +3352,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3359,122 +3362,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>308</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3529,17 +3532,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3554,7 +3557,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3564,7 +3567,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3579,7 +3582,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3589,7 +3592,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3604,7 +3607,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3614,7 +3617,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3629,7 +3632,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3639,7 +3642,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3654,7 +3657,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Summary.xlsx
+++ b/GPIpuget/project/Summary.xlsx
@@ -401,7 +401,7 @@
     <t>project_netlist_path</t>
   </si>
   <si>
-    <t>/tmp/GPIpuget.net</t>
+    <t>/portal/web/api/utils/hopper/tests/GPIpuget.net</t>
   </si>
   <si>
     <t>gen_reports</t>
